--- a/Data-paper/tables-baboonFA.xlsx
+++ b/Data-paper/tables-baboonFA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Research-In Review\Baboon FA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KARAH\Desktop\baboon-stress\data-paper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D356B953-77BC-41F4-BB1A-BC6A90AE58A6}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{691C9820-0EF8-4731-85C7-C21A3BEF58A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="56870" yWindow="910" windowWidth="19120" windowHeight="19740" activeTab="2" xr2:uid="{EE5F91EA-4A4C-4EFB-9CBC-BAA47D0C4EEA}"/>
+    <workbookView xWindow="8565" yWindow="945" windowWidth="16320" windowHeight="13275" activeTab="2" xr2:uid="{EE5F91EA-4A4C-4EFB-9CBC-BAA47D0C4EEA}"/>
   </bookViews>
   <sheets>
     <sheet name="T1-ME summary" sheetId="10" r:id="rId1"/>
@@ -272,11 +272,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
@@ -290,7 +289,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -303,10 +301,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -316,7 +314,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -326,17 +323,12 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
@@ -358,9 +350,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -398,7 +390,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -504,7 +496,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -646,7 +638,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -655,221 +647,221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55540D9A-0EAF-4494-8C2B-1A477D0A156A}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="9.26171875" defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.15625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.15625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5234375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.15625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.89453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.20703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.05078125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="10" customFormat="1" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:7" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="3">
         <v>0.11521263669501824</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="3">
         <v>0.24673168927569125</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>0.22337149947283153</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="3">
         <v>9.5147260796581715E-2</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="3">
         <v>0.50872359963269054</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="3">
         <v>0.41357633883610889</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>0.12047619047619047</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="3">
         <v>0.23601432982136256</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>0.22215411558669002</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <v>9.1259500542888145E-2</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="3">
         <v>0.47293866096485365</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="3">
         <v>0.38167916042196554</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>6.7333333333333328E-2</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>0.15839271396463731</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>0.15615873015873016</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <v>4.544600938967136E-2</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="3">
         <v>0.33166666666666672</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="3">
         <v>0.28622065727699536</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>6.5882352941176461E-2</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>0.18193969783066116</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>0.16397688356164383</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>6.5882352941176461E-2</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <v>0.36506550218340605</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="3">
         <v>0.29918314924222961</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="3">
         <v>7.5333333333333335E-2</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>0.18277593083104207</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>0.14972941176470589</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>5.3538461538461528E-2</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <v>0.5099999999999999</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="3">
         <v>0.45646153846153836</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="3">
         <v>5.909090909090909E-2</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <v>0.13331716324163145</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <v>0.11771140207310421</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <v>4.5806451612903226E-2</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="3">
         <v>0.35857142857142854</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="3">
         <v>0.31276497695852529</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="3">
         <v>3.6000000000000004E-2</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="3">
         <v>0.10336379101897658</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>9.3556547619047623E-2</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="3">
         <v>3.6000000000000004E-2</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="3">
         <v>0.30499999999999999</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="3">
         <v>0.26899999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>4.0606060606060604E-2</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>8.463742506172274E-2</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>7.7252747252747236E-2</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>2.8552631578947368E-2</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <v>0.20818181818181819</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="5">
         <v>0.17962918660287083</v>
       </c>
     </row>
@@ -882,556 +874,556 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{509603D4-A48C-4EDD-A2F1-2BD976E607F6}">
   <dimension ref="A1:E32"/>
-  <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.3671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.7890625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.3125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="2.68359375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="18" t="s">
+      <c r="B2" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="17">
         <v>6.2767000000000005E-3</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="18" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="18" t="s">
+      <c r="B3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="17">
         <v>1.0457000000000001E-2</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="18" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="18" t="s">
+      <c r="B4" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="17">
         <v>8.5620000000000002E-3</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="18" t="s">
+      <c r="B5" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="17">
         <v>4.4386E-3</v>
       </c>
-      <c r="E5" s="23">
+      <c r="E5">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="18" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="18" t="s">
+      <c r="B6" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="17">
         <v>1.15709E-2</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="18" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="18" t="s">
+      <c r="B7" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="17">
         <v>8.9099999999999995E-3</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="18" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="18" t="s">
+      <c r="B8" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="17">
         <v>2.8579E-2</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="18" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="18" t="s">
+      <c r="B9" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="17">
         <v>3.9489999999999997E-2</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="18" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="18" t="s">
+      <c r="B10" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="17">
         <v>1.3246999999999998E-2</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="18" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="17">
         <v>3.8048999999999999E-2</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="18" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="17">
         <v>5.5677999999999991E-2</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="18" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="17">
         <v>2.3969000000000001E-2</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E13">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="18" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="17">
         <v>4.3601999999999995E-2</v>
       </c>
-      <c r="E14" s="23">
+      <c r="E14">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="18" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="17">
         <v>2.8692000000000002E-2</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E15">
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="18" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="17">
         <v>3.9558999999999997E-2</v>
       </c>
-      <c r="E16" s="23">
+      <c r="E16">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="18" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="17">
         <v>4.8283E-2</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="18" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="18" t="s">
+      <c r="B18" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="17">
         <v>1.0606000000000001E-2</v>
       </c>
-      <c r="E18" s="23">
+      <c r="E18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A19" s="18" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="18" t="s">
+      <c r="B19" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="17">
         <v>3.0541000000000002E-2</v>
       </c>
-      <c r="E19" s="23">
+      <c r="E19">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A20" s="18" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="18" t="s">
+      <c r="B20" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="17">
         <v>8.4099999999999991E-3</v>
       </c>
-      <c r="E20" s="23">
+      <c r="E20">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A21" s="18" t="s">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="18" t="s">
+      <c r="B21" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="17">
         <v>7.9830000000000005E-3</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A22" s="18" t="s">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="18" t="s">
+      <c r="B22" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="17">
         <v>7.2766999999999997E-3</v>
       </c>
-      <c r="E22" s="23">
+      <c r="E22">
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A23" s="18" t="s">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" s="18" t="s">
+      <c r="B23" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="17">
         <v>2.0684000000000001E-2</v>
       </c>
-      <c r="E23" s="23">
+      <c r="E23">
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A24" s="18" t="s">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="18" t="s">
+      <c r="B24" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="17">
         <v>1.7562000000000001E-2</v>
       </c>
-      <c r="E24" s="23">
+      <c r="E24">
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A25" s="18" t="s">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="18" t="s">
+      <c r="B25" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="17">
         <v>3.1292E-2</v>
       </c>
-      <c r="E25" s="23">
+      <c r="E25">
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A26" s="18" t="s">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C26" s="18" t="s">
+      <c r="B26" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="17">
         <v>2.1019000000000003E-2</v>
       </c>
-      <c r="E26" s="23">
+      <c r="E26">
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A27" s="18" t="s">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="17">
         <v>7.5737000000000013E-2</v>
       </c>
-      <c r="E27" s="23">
+      <c r="E27">
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A28" s="18" t="s">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="17">
         <v>6.6650000000000001E-2</v>
       </c>
-      <c r="E28" s="23">
+      <c r="E28">
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A29" s="18" t="s">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="17">
         <v>5.0460999999999999E-2</v>
       </c>
-      <c r="E29" s="23">
+      <c r="E29">
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A30" s="18" t="s">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="17">
         <v>7.0930999999999994E-2</v>
       </c>
-      <c r="E30" s="23">
+      <c r="E30">
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A31" s="18" t="s">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="17">
         <v>7.9821000000000003E-2</v>
       </c>
-      <c r="E31" s="23">
+      <c r="E31">
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A32" s="20" t="s">
+    <row r="32" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B32" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C32" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="21">
+      <c r="D32" s="19">
         <v>9.9453999999999987E-2</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="4">
         <v>29</v>
       </c>
     </row>
@@ -1443,89 +1435,89 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{074BC804-E8ED-42E2-9C1A-2DA6E1FE9D52}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.05078125" customWidth="1"/>
-    <col min="2" max="2" width="7.05078125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.15625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.89453125" customWidth="1"/>
-    <col min="5" max="5" width="8.89453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1015625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.05078125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.5234375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.3671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.68359375" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="1.3671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="1.734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="1.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="1.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="10" customFormat="1" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:4" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="1">
         <v>1.7797000000000001</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="1">
         <v>8</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="1">
         <v>0.13569999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="1">
         <v>0.19089999999999999</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="1">
         <v>1</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="1">
         <v>0.66539999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="23" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="1">
         <v>0.26</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="1">
         <v>1</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="1">
         <v>0.61</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="10">
         <v>8.484</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="10">
         <v>1</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="29">
         <v>6.829E-3</v>
       </c>
     </row>
@@ -1540,147 +1532,143 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74A40FE7-0E96-4C0D-B32C-424289DCF12F}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.1015625" customWidth="1"/>
-    <col min="2" max="2" width="21.26171875" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.5234375" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.15625" style="22" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="2.47265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.15625" style="22" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.3125" style="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.1015625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:7" s="6" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A1" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="26"/>
-    </row>
-    <row r="2" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="27" t="s">
+      <c r="G1" s="23"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="28">
+      <c r="D2" s="20">
         <v>10.602</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2" s="33">
+      <c r="F2" s="27">
         <v>2.875E-3</v>
       </c>
-      <c r="G2" s="29"/>
-    </row>
-    <row r="3" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="27" t="s">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="28">
+      <c r="D3" s="20">
         <v>1.6696</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3">
         <v>1</v>
       </c>
-      <c r="F3" s="28">
+      <c r="F3" s="20">
         <v>0.20649999999999999</v>
       </c>
-      <c r="G3" s="29"/>
-    </row>
-    <row r="4" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="27"/>
-      <c r="B4" s="27" t="s">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="20">
         <v>6.6959</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4">
         <v>3</v>
       </c>
-      <c r="F4" s="33">
+      <c r="F4" s="27">
         <v>1.5939999999999999E-3</v>
       </c>
-      <c r="G4" s="29"/>
-    </row>
-    <row r="5" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="27" t="s">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="20">
         <v>6.3799999999999996E-2</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="20">
         <v>0.80230000000000001</v>
       </c>
-      <c r="G5" s="29"/>
-    </row>
-    <row r="6" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B6" s="30" t="s">
+    </row>
+    <row r="6" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="25">
         <v>4.3127000000000004</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>3</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="28">
         <v>1.312E-2</v>
       </c>
-      <c r="G6" s="32"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="E7" s="22"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="E8" s="22"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="E9" s="22"/>
+      <c r="G6" s="26"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E7" s="20"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E8" s="20"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E9" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
